--- a/data/marketplace/MarketplaceSitecoreDocsData.xlsx
+++ b/data/marketplace/MarketplaceSitecoreDocsData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_9AEFC13B1E19F94F066002CD709186ADA028F88C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2BB7E2-A3B8-42C6-9E99-D82E5B5CD51D}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_9AEFC13B1E19F94F066002CD709186ADA028F88C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705EC32F-225D-4444-91D8-6A1088A07532}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10216,9 +10216,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
         <v>677</v>
@@ -10299,9 +10299,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
         <v>694</v>
@@ -10382,9 +10382,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
         <v>705</v>
@@ -10465,9 +10465,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
         <v>716</v>
@@ -10548,9 +10548,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
         <v>727</v>
@@ -10631,9 +10631,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
         <v>738</v>
@@ -10714,9 +10714,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
         <v>749</v>
@@ -10797,9 +10797,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
         <v>760</v>
@@ -10880,9 +10880,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
         <v>771</v>
@@ -10963,9 +10963,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
         <v>782</v>
@@ -11046,9 +11046,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
         <v>793</v>
@@ -11129,9 +11129,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
         <v>804</v>
@@ -11212,9 +11212,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
         <v>815</v>
@@ -11295,9 +11295,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
         <v>826</v>
@@ -11378,9 +11378,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1963</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
         <v>837</v>
@@ -14366,9 +14366,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B98" t="s">
         <v>1236</v>
@@ -14449,9 +14449,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B99" t="s">
         <v>1253</v>
@@ -14532,9 +14532,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B100" t="s">
         <v>1267</v>
@@ -14615,9 +14615,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B101" t="s">
         <v>1277</v>
@@ -14698,9 +14698,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B102" t="s">
         <v>1287</v>
@@ -14781,9 +14781,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B103" t="s">
         <v>1297</v>
@@ -14864,9 +14864,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B104" t="s">
         <v>1307</v>
@@ -14947,9 +14947,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B105" t="s">
         <v>1317</v>
@@ -15030,9 +15030,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B106" t="s">
         <v>1327</v>
@@ -15113,9 +15113,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B107" t="s">
         <v>1337</v>
@@ -15196,9 +15196,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B108" t="s">
         <v>1347</v>
@@ -15279,9 +15279,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B109" t="s">
         <v>1358</v>
@@ -15362,9 +15362,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B110" t="s">
         <v>1369</v>
@@ -15445,9 +15445,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B111" t="s">
         <v>1380</v>
@@ -15528,9 +15528,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B112" t="s">
         <v>1391</v>
@@ -15611,9 +15611,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B113" t="s">
         <v>1402</v>
@@ -15694,9 +15694,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B114" t="s">
         <v>1413</v>
@@ -15777,9 +15777,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B115" t="s">
         <v>1424</v>
@@ -15860,9 +15860,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B116" t="s">
         <v>1435</v>
@@ -15943,9 +15943,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B117" t="s">
         <v>1446</v>
@@ -16026,9 +16026,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B118" t="s">
         <v>1456</v>
@@ -16109,9 +16109,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B119" t="s">
         <v>1466</v>
@@ -16192,9 +16192,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B120" t="s">
         <v>1476</v>
@@ -16275,9 +16275,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B121" t="s">
         <v>1486</v>
@@ -16358,9 +16358,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B122" t="s">
         <v>1496</v>
@@ -16441,9 +16441,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B123" t="s">
         <v>1506</v>
@@ -16524,9 +16524,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B124" t="s">
         <v>1517</v>
@@ -16607,9 +16607,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B125" t="s">
         <v>1528</v>
@@ -16690,9 +16690,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B126" t="s">
         <v>1539</v>
@@ -16773,9 +16773,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B127" t="s">
         <v>1554</v>
@@ -16856,9 +16856,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B128" t="s">
         <v>1565</v>
@@ -16939,9 +16939,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B129" t="s">
         <v>1576</v>
@@ -17022,9 +17022,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B130" t="s">
         <v>1587</v>
@@ -17105,9 +17105,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B131" t="s">
         <v>1598</v>
@@ -17188,9 +17188,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B132" t="s">
         <v>1612</v>
@@ -17271,9 +17271,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B133" t="s">
         <v>1622</v>
@@ -17354,9 +17354,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B134" t="s">
         <v>1632</v>
@@ -17437,9 +17437,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B135" t="s">
         <v>1642</v>
@@ -17520,9 +17520,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B136" t="s">
         <v>1652</v>
@@ -17603,9 +17603,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B137" t="s">
         <v>1662</v>
@@ -17686,9 +17686,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B138" t="s">
         <v>1672</v>
@@ -17769,9 +17769,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B139" t="s">
         <v>1682</v>
@@ -17852,9 +17852,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B140" t="s">
         <v>1692</v>
@@ -17935,9 +17935,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B141" t="s">
         <v>1703</v>
@@ -18018,9 +18018,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B142" t="s">
         <v>1714</v>
@@ -18101,9 +18101,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B143" t="s">
         <v>1725</v>
@@ -18184,9 +18184,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B144" t="s">
         <v>1736</v>
@@ -18267,9 +18267,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B145" t="s">
         <v>1747</v>
@@ -18350,9 +18350,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B146" t="s">
         <v>1758</v>
@@ -18433,9 +18433,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B147" t="s">
         <v>1769</v>
@@ -18516,9 +18516,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B148" t="s">
         <v>1780</v>
@@ -18599,9 +18599,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B149" t="s">
         <v>1794</v>
@@ -18682,9 +18682,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B150" t="s">
         <v>1804</v>
@@ -18765,9 +18765,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B151" t="s">
         <v>1814</v>
@@ -18848,9 +18848,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B152" t="s">
         <v>1824</v>
@@ -18931,9 +18931,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B153" t="s">
         <v>1834</v>
@@ -19014,9 +19014,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B154" t="s">
         <v>1845</v>
@@ -19097,9 +19097,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B155" t="s">
         <v>1855</v>
@@ -19180,9 +19180,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B156" t="s">
         <v>1865</v>
@@ -19263,9 +19263,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B157" t="s">
         <v>1875</v>
@@ -19346,9 +19346,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B158" t="s">
         <v>1886</v>
@@ -19429,9 +19429,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B159" t="s">
         <v>1897</v>
@@ -19512,9 +19512,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B160" t="s">
         <v>1908</v>
@@ -19595,9 +19595,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B161" t="s">
         <v>1919</v>
@@ -19678,9 +19678,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B162" t="s">
         <v>1930</v>
@@ -19761,9 +19761,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B163" t="s">
         <v>1941</v>
@@ -19844,9 +19844,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>27</v>
+        <v>1963</v>
       </c>
       <c r="B164" t="s">
         <v>1952</v>
@@ -19931,7 +19931,7 @@
   <autoFilter ref="A1:AA164" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="TX"/>
+        <filter val="WA"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19940,4 +19940,10 @@
     <ignoredError sqref="A1:AA1 B3:AA164 B2:AA2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" enabled="0" method="" siteId="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/data/marketplace/MarketplaceSitecoreDocsData.xlsx
+++ b/data/marketplace/MarketplaceSitecoreDocsData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/marketplace/data/marketplace/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/seeram_tarunvardhan_molinahealthcare_com/Documents/Desktop/Automationss/IMP/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_9AEFC13BD289BD60AA6102CD709186ADA0296ED9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21B8348D-A753-4D36-A9ED-40023C1A8935}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{AA5DDFBF-1896-4DF1-B708-DD396739933E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D0A0943-20D5-4FC0-BF49-E0AF46DE81F1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SitecoreDocs" sheetId="1" r:id="rId1"/>
@@ -6341,7 +6341,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6357,6 +6357,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6366,7 +6371,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -6374,14 +6379,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6722,38 +6744,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD172"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" customWidth="1"/>
-    <col min="4" max="5" width="14.796875" customWidth="1"/>
-    <col min="6" max="6" width="28.796875" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="110.796875" customWidth="1"/>
-    <col min="12" max="12" width="17.796875" customWidth="1"/>
-    <col min="13" max="14" width="28.796875" customWidth="1"/>
-    <col min="15" max="16" width="110.796875" customWidth="1"/>
-    <col min="17" max="17" width="17.796875" customWidth="1"/>
-    <col min="18" max="19" width="28.796875" customWidth="1"/>
-    <col min="20" max="20" width="63.09765625" customWidth="1"/>
-    <col min="21" max="21" width="65.19921875" customWidth="1"/>
-    <col min="22" max="22" width="17.796875" customWidth="1"/>
-    <col min="23" max="23" width="18.3984375" customWidth="1"/>
+    <col min="10" max="11" width="110.83203125" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" customWidth="1"/>
+    <col min="13" max="14" width="28.83203125" customWidth="1"/>
+    <col min="15" max="16" width="110.83203125" customWidth="1"/>
+    <col min="17" max="17" width="17.83203125" customWidth="1"/>
+    <col min="18" max="19" width="28.83203125" customWidth="1"/>
+    <col min="20" max="20" width="63.08203125" customWidth="1"/>
+    <col min="21" max="21" width="65.1640625" customWidth="1"/>
+    <col min="22" max="22" width="17.83203125" customWidth="1"/>
+    <col min="23" max="23" width="18.4140625" customWidth="1"/>
     <col min="24" max="24" width="19" customWidth="1"/>
-    <col min="25" max="25" width="19.69921875" customWidth="1"/>
-    <col min="26" max="26" width="20.09765625" customWidth="1"/>
-    <col min="27" max="27" width="14.796875" customWidth="1"/>
-    <col min="28" max="28" width="15.796875" customWidth="1"/>
-    <col min="29" max="29" width="11.796875" customWidth="1"/>
-    <col min="30" max="30" width="16.796875" customWidth="1"/>
+    <col min="25" max="25" width="19.6640625" customWidth="1"/>
+    <col min="26" max="26" width="20.08203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
+    <col min="28" max="28" width="15.83203125" customWidth="1"/>
+    <col min="29" max="29" width="11.83203125" customWidth="1"/>
+    <col min="30" max="30" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6845,9 +6866,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -6937,9 +6958,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -7029,9 +7050,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
@@ -7121,9 +7142,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
         <v>86</v>
@@ -7213,9 +7234,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>101</v>
@@ -7305,9 +7326,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>116</v>
@@ -7397,9 +7418,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>131</v>
@@ -7489,9 +7510,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>146</v>
@@ -7581,9 +7602,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>161</v>
@@ -7673,9 +7694,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>176</v>
@@ -7765,7 +7786,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2055</v>
       </c>
@@ -7857,7 +7878,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>2055</v>
       </c>
@@ -7949,7 +7970,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2055</v>
       </c>
@@ -8041,7 +8062,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>2055</v>
       </c>
@@ -8133,7 +8154,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>2055</v>
       </c>
@@ -8225,7 +8246,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>2055</v>
       </c>
@@ -8317,7 +8338,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>2055</v>
       </c>
@@ -8409,7 +8430,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>2055</v>
       </c>
@@ -8501,7 +8522,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>2055</v>
       </c>
@@ -8593,7 +8614,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>2055</v>
       </c>
@@ -8685,7 +8706,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2055</v>
       </c>
@@ -8777,7 +8798,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>2055</v>
       </c>
@@ -8869,7 +8890,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>2055</v>
       </c>
@@ -8961,7 +8982,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>2055</v>
       </c>
@@ -9053,7 +9074,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>2055</v>
       </c>
@@ -9145,7 +9166,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>2055</v>
       </c>
@@ -9237,7 +9258,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>2055</v>
       </c>
@@ -9329,7 +9350,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>2055</v>
       </c>
@@ -9421,7 +9442,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>2055</v>
       </c>
@@ -9513,7 +9534,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>2055</v>
       </c>
@@ -9605,7 +9626,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2055</v>
       </c>
@@ -9697,7 +9718,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>2055</v>
       </c>
@@ -9789,7 +9810,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>2055</v>
       </c>
@@ -9881,9 +9902,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
         <v>536</v>
@@ -9973,9 +9994,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="36" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
         <v>550</v>
@@ -10065,9 +10086,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="37" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
         <v>561</v>
@@ -10157,9 +10178,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="38" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
         <v>572</v>
@@ -10249,9 +10270,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="39" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
         <v>583</v>
@@ -10341,9 +10362,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="40" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
         <v>594</v>
@@ -10433,9 +10454,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="41" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
         <v>605</v>
@@ -10525,9 +10546,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="42" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
         <v>616</v>
@@ -10617,9 +10638,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="43" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
         <v>627</v>
@@ -10709,9 +10730,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="44" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B44" t="s">
         <v>638</v>
@@ -10801,7 +10822,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="45" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>2055</v>
       </c>
@@ -10893,7 +10914,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="46" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>2055</v>
       </c>
@@ -10985,7 +11006,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="47" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>2055</v>
       </c>
@@ -11077,9 +11098,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="48" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
         <v>682</v>
@@ -11105,7 +11126,7 @@
       <c r="I48" t="s">
         <v>688</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="2" t="s">
         <v>689</v>
       </c>
       <c r="K48" t="s">
@@ -11169,9 +11190,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="49" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
         <v>700</v>
@@ -11197,7 +11218,7 @@
       <c r="I49" t="s">
         <v>704</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="2" t="s">
         <v>705</v>
       </c>
       <c r="K49" t="s">
@@ -11261,9 +11282,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="50" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
         <v>711</v>
@@ -11289,7 +11310,7 @@
       <c r="I50" t="s">
         <v>715</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="2" t="s">
         <v>716</v>
       </c>
       <c r="K50" t="s">
@@ -11353,9 +11374,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="51" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
         <v>722</v>
@@ -11381,7 +11402,7 @@
       <c r="I51" t="s">
         <v>726</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="2" t="s">
         <v>727</v>
       </c>
       <c r="K51" t="s">
@@ -11445,9 +11466,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="52" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
         <v>733</v>
@@ -11473,7 +11494,7 @@
       <c r="I52" t="s">
         <v>737</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="2" t="s">
         <v>738</v>
       </c>
       <c r="K52" t="s">
@@ -11537,9 +11558,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="53" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
         <v>744</v>
@@ -11565,7 +11586,7 @@
       <c r="I53" t="s">
         <v>748</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="2" t="s">
         <v>749</v>
       </c>
       <c r="K53" t="s">
@@ -11629,9 +11650,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="54" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
         <v>755</v>
@@ -11657,7 +11678,7 @@
       <c r="I54" t="s">
         <v>759</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="3" t="s">
         <v>760</v>
       </c>
       <c r="K54" t="s">
@@ -11721,9 +11742,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="55" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
         <v>766</v>
@@ -11749,7 +11770,7 @@
       <c r="I55" t="s">
         <v>770</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="2" t="s">
         <v>771</v>
       </c>
       <c r="K55" t="s">
@@ -11813,9 +11834,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="56" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
         <v>777</v>
@@ -11841,7 +11862,7 @@
       <c r="I56" t="s">
         <v>781</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="2" t="s">
         <v>782</v>
       </c>
       <c r="K56" t="s">
@@ -11905,9 +11926,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="57" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
         <v>788</v>
@@ -11933,7 +11954,7 @@
       <c r="I57" t="s">
         <v>792</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="2" t="s">
         <v>793</v>
       </c>
       <c r="K57" t="s">
@@ -11997,7 +12018,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="58" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>2055</v>
       </c>
@@ -12025,7 +12046,7 @@
       <c r="I58" t="s">
         <v>803</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="2" t="s">
         <v>804</v>
       </c>
       <c r="K58" t="s">
@@ -12089,7 +12110,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="59" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>2055</v>
       </c>
@@ -12117,7 +12138,7 @@
       <c r="I59" t="s">
         <v>814</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="2" t="s">
         <v>815</v>
       </c>
       <c r="K59" t="s">
@@ -12181,7 +12202,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="60" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>2055</v>
       </c>
@@ -12209,7 +12230,7 @@
       <c r="I60" t="s">
         <v>825</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="2" t="s">
         <v>826</v>
       </c>
       <c r="K60" t="s">
@@ -12273,7 +12294,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="61" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>2055</v>
       </c>
@@ -12301,7 +12322,7 @@
       <c r="I61" t="s">
         <v>836</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="2" t="s">
         <v>837</v>
       </c>
       <c r="K61" t="s">
@@ -12365,7 +12386,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="62" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>2055</v>
       </c>
@@ -12393,7 +12414,7 @@
       <c r="I62" t="s">
         <v>847</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="2" t="s">
         <v>848</v>
       </c>
       <c r="K62" t="s">
@@ -12457,9 +12478,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="63" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B63" t="s">
         <v>854</v>
@@ -12549,9 +12570,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="64" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
         <v>871</v>
@@ -12641,9 +12662,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="65" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
         <v>882</v>
@@ -12733,9 +12754,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="66" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B66" t="s">
         <v>893</v>
@@ -12825,9 +12846,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="67" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
         <v>904</v>
@@ -12917,9 +12938,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="68" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
         <v>915</v>
@@ -13009,9 +13030,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="69" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
         <v>926</v>
@@ -13101,9 +13122,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="70" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
         <v>937</v>
@@ -13193,9 +13214,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="71" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
         <v>948</v>
@@ -13285,9 +13306,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="72" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B72" t="s">
         <v>959</v>
@@ -13377,7 +13398,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="73" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>2055</v>
       </c>
@@ -13469,7 +13490,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="74" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>2055</v>
       </c>
@@ -13561,7 +13582,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="75" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>2055</v>
       </c>
@@ -13653,7 +13674,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="76" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>2055</v>
       </c>
@@ -13745,7 +13766,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="77" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>2055</v>
       </c>
@@ -13837,7 +13858,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="78" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>2055</v>
       </c>
@@ -13929,7 +13950,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="79" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>2055</v>
       </c>
@@ -14021,7 +14042,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="80" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>2055</v>
       </c>
@@ -14113,7 +14134,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="81" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>2055</v>
       </c>
@@ -14205,7 +14226,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="82" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>2055</v>
       </c>
@@ -14297,7 +14318,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="83" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>2055</v>
       </c>
@@ -14389,7 +14410,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="84" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>2055</v>
       </c>
@@ -14481,7 +14502,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="85" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>2055</v>
       </c>
@@ -14573,7 +14594,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="86" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>2055</v>
       </c>
@@ -14665,7 +14686,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="87" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>2055</v>
       </c>
@@ -14757,7 +14778,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="88" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>2055</v>
       </c>
@@ -14849,9 +14870,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="89" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B89" t="s">
         <v>1146</v>
@@ -14941,9 +14962,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="90" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
         <v>1162</v>
@@ -15033,9 +15054,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="91" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
         <v>1172</v>
@@ -15125,9 +15146,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="92" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B92" t="s">
         <v>1182</v>
@@ -15217,9 +15238,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="93" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B93" t="s">
         <v>1192</v>
@@ -15309,9 +15330,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="94" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B94" t="s">
         <v>1202</v>
@@ -15401,9 +15422,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="95" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B95" t="s">
         <v>1212</v>
@@ -15493,9 +15514,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="96" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B96" t="s">
         <v>1222</v>
@@ -15585,9 +15606,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="97" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B97" t="s">
         <v>1232</v>
@@ -15677,9 +15698,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="98" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B98" t="s">
         <v>1242</v>
@@ -15769,7 +15790,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="99" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>2055</v>
       </c>
@@ -15861,7 +15882,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="100" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>2055</v>
       </c>
@@ -15953,7 +15974,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="101" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>2055</v>
       </c>
@@ -16045,7 +16066,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="102" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>2055</v>
       </c>
@@ -16137,9 +16158,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="103" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B103" t="s">
         <v>1304</v>
@@ -16229,9 +16250,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="104" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
         <v>1314</v>
@@ -16321,9 +16342,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="105" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B105" t="s">
         <v>1324</v>
@@ -16413,9 +16434,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="106" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B106" t="s">
         <v>1334</v>
@@ -16505,9 +16526,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="107" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B107" t="s">
         <v>1344</v>
@@ -16597,9 +16618,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="108" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B108" t="s">
         <v>1354</v>
@@ -16689,9 +16710,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="109" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B109" t="s">
         <v>1365</v>
@@ -16781,9 +16802,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="110" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B110" t="s">
         <v>1376</v>
@@ -16873,9 +16894,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="111" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B111" t="s">
         <v>1387</v>
@@ -16965,9 +16986,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="112" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B112" t="s">
         <v>1398</v>
@@ -17057,7 +17078,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="113" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>2055</v>
       </c>
@@ -17149,7 +17170,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="114" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>2055</v>
       </c>
@@ -17241,7 +17262,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="115" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>2055</v>
       </c>
@@ -17333,7 +17354,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="116" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>2055</v>
       </c>
@@ -17425,7 +17446,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="117" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>2055</v>
       </c>
@@ -17517,7 +17538,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="118" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>2055</v>
       </c>
@@ -17609,7 +17630,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="119" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>2055</v>
       </c>
@@ -17701,7 +17722,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="120" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>2055</v>
       </c>
@@ -17793,7 +17814,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="121" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>2055</v>
       </c>
@@ -17885,7 +17906,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="122" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>2055</v>
       </c>
@@ -17977,7 +17998,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="123" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>2055</v>
       </c>
@@ -18069,7 +18090,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="124" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>2055</v>
       </c>
@@ -18161,7 +18182,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="125" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>2055</v>
       </c>
@@ -18253,7 +18274,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="126" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>2055</v>
       </c>
@@ -18345,7 +18366,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="127" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>2055</v>
       </c>
@@ -18437,7 +18458,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="128" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>2055</v>
       </c>
@@ -18529,7 +18550,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="129" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>2055</v>
       </c>
@@ -18621,7 +18642,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="130" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>2055</v>
       </c>
@@ -18713,7 +18734,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="131" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>2055</v>
       </c>
@@ -18805,7 +18826,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="132" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>2055</v>
       </c>
@@ -18897,7 +18918,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="133" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>2055</v>
       </c>
@@ -18989,7 +19010,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="134" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>2055</v>
       </c>
@@ -19081,7 +19102,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="135" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>2055</v>
       </c>
@@ -19173,7 +19194,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="136" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>2055</v>
       </c>
@@ -19265,7 +19286,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="137" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>2055</v>
       </c>
@@ -19357,9 +19378,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="138" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B138" t="s">
         <v>1679</v>
@@ -19449,9 +19470,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="139" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B139" t="s">
         <v>1689</v>
@@ -19541,9 +19562,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="140" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B140" t="s">
         <v>1699</v>
@@ -19633,9 +19654,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="141" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B141" t="s">
         <v>1710</v>
@@ -19725,9 +19746,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="142" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B142" t="s">
         <v>1721</v>
@@ -19817,9 +19838,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="143" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B143" t="s">
         <v>1732</v>
@@ -19909,9 +19930,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="144" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B144" t="s">
         <v>1743</v>
@@ -20001,9 +20022,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="145" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B145" t="s">
         <v>1754</v>
@@ -20093,9 +20114,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="146" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B146" t="s">
         <v>1765</v>
@@ -20185,9 +20206,9 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="147" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>2055</v>
+        <v>30</v>
       </c>
       <c r="B147" t="s">
         <v>1776</v>
@@ -20277,7 +20298,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="148" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>2055</v>
       </c>
@@ -20369,7 +20390,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="149" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>2055</v>
       </c>
@@ -20461,7 +20482,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="150" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>2055</v>
       </c>
@@ -20553,7 +20574,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="151" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>2055</v>
       </c>
@@ -20645,7 +20666,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="152" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>2055</v>
       </c>
@@ -20737,7 +20758,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>2055</v>
       </c>
@@ -20829,7 +20850,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="154" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>2055</v>
       </c>
@@ -20921,7 +20942,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="155" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>2055</v>
       </c>
@@ -21013,7 +21034,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="156" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>2055</v>
       </c>
@@ -21105,7 +21126,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="157" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>2055</v>
       </c>
@@ -21197,7 +21218,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="158" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>2055</v>
       </c>
@@ -21289,7 +21310,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="159" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>2055</v>
       </c>
@@ -21381,7 +21402,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="160" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>2055</v>
       </c>
@@ -21473,7 +21494,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="161" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>2055</v>
       </c>
@@ -21565,7 +21586,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="162" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>2055</v>
       </c>
@@ -21657,7 +21678,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="163" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>2055</v>
       </c>
@@ -21749,7 +21770,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="164" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>2055</v>
       </c>
@@ -21841,7 +21862,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="165" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>30</v>
       </c>
@@ -21933,7 +21954,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="166" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>30</v>
       </c>
@@ -22025,7 +22046,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="167" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>30</v>
       </c>
@@ -22117,7 +22138,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="168" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>30</v>
       </c>
@@ -22209,7 +22230,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="169" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>30</v>
       </c>
@@ -22301,7 +22322,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="170" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>30</v>
       </c>
@@ -22393,7 +22414,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="171" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>30</v>
       </c>
@@ -22485,7 +22506,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="172" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>30</v>
       </c>
@@ -22578,28 +22599,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD172" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="FL"/>
-        <filter val="IL"/>
-        <filter val="KY"/>
-        <filter val="MI"/>
-        <filter val="MS"/>
-        <filter val="OH"/>
-        <filter val="SC"/>
-        <filter val="UT"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AD172" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="AD165" r:id="rId1" xr:uid="{AC5603BE-EFE3-4CA2-96E0-F946A8894D30}"/>
     <hyperlink ref="AD166:AD172" r:id="rId2" display="https://uat-pws.molinahealthcare.com/" xr:uid="{C10BB269-8BF9-4251-A8EC-5DF8C1E3DF61}"/>
     <hyperlink ref="J165" r:id="rId3" display="https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/sbc/2027/english/UT27SBCE_G1_0.pdf" xr:uid="{C4D7216F-578A-42A5-8993-805593874C4F}"/>
+    <hyperlink ref="J54" r:id="rId4" xr:uid="{EDC94E02-241F-42DC-9985-6C648668A4E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AD1 B172:I172 B165:I165 B63:AD164 B48:AD48 B49:AD62 B35:AD47 B2:AD2 B3:AD34 L165:N165 Q165:S165 V165:AC165 B166:I166 L166:N166 Q166:S166 V166:AC166 B167:I167 L167:N167 Q167:S167 V167:AC167 B168:I168 L168:N168 Q168:S168 V168:AC168 B169:I169 L169:N169 Q169:S169 V169:AC169 B170:I170 L170:N170 Q170:S170 V170:AC170 B171:I171 L171:N171 Q171:S171 V171:AC171 L172:N172 Q172:S172 V172:AC172" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AD1 B172:I172 B165:I165 B63:AD164 B48:I48 B49:I62 B35:AD47 B2:AD2 B3:AD34 L165:N165 Q165:S165 V165:AC165 B166:I166 L166:N166 Q166:S166 V166:AC166 B167:I167 L167:N167 Q167:S167 V167:AC167 B168:I168 L168:N168 Q168:S168 V168:AC168 B169:I169 L169:N169 Q169:S169 V169:AC169 B170:I170 L170:N170 Q170:S170 V170:AC170 B171:I171 L171:N171 Q171:S171 V171:AC171 L172:N172 Q172:S172 V172:AC172 K48:AD48 K49:AD62" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" enabled="0" method="" siteId="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/data/marketplace/MarketplaceSitecoreDocsData.xlsx
+++ b/data/marketplace/MarketplaceSitecoreDocsData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/seeram_tarunvardhan_molinahealthcare_com/Documents/Desktop/Automationss/IMP/marketplace/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{AA5DDFBF-1896-4DF1-B708-DD396739933E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D0A0943-20D5-4FC0-BF49-E0AF46DE81F1}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{11E98B66-419E-441D-9EF9-433F83B9C807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA0DD2F5-0C32-4101-8AF7-75D69FD48EFA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5160" uniqueCount="2104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5030" uniqueCount="2104">
   <si>
     <t>Run</t>
   </si>
@@ -6193,148 +6193,148 @@
     <t>N</t>
   </si>
   <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/sbc/2027/english/UT27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/sbc/2027/spanish/UT27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/SOB/2027/english/UT27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/SOB/2027/spanish/UT27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/EOC/2027/english/UT27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/EOC/2027/spanish/UT27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/sbc/2027/english/IL27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/sbc/2027/spanish/IL27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/EOC/2027/english/IL27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/EOC/2027/spanish/IL27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/sbc/2027/english/MI27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/sbc/2027/spanish/MI27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/english/MI27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/spanish/MI27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/EOC/2027/english/MI27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/EOC/2027/spanish/MI27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/sbc/2027/english/SC27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/sbc/2027/spanish/SC27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/SOB/2027/english/SC27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/SOB/2027/spanish/SC27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/EOC/2027/english/SC27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/EOC/2027/spanish/SC27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/sbc/2027/english/FL27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/sbc/2027/spanish/FL27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/SOB/2027/english/FL27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/SOB/2027/spanish/FL27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/EOC/2027/english/FL27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/EOC/2027/spanish/FL27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/EOC/2027/english/OH27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/EOC/2027/spanish/OH27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/sbc/2027/english/KY27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/sbc/2027/spanish/KY27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/SOB/2027/english/KY27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/SOB/2027/spanish/KY27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/EOC/2027/english/KY27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/EOC/2027/spanish/KY27EOCS_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/sbc/2027/english/MS27SBCE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/sbc/2027/spanish/MS27SBCS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/SOB/2027/english/MS27SOBE_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/SOB/2027/spanish/MS27SOBS_G1_0.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/EOC/2027/english/MS27EOCE_OX.pdf</t>
-  </si>
-  <si>
-    <t>https://uat-pws.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/EOC/2027/spanish/MS27EOCS_OX.pdf</t>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/sbc/2027/english/UT27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/sbc/2027/spanish/UT27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/sbc/2027/english/IL27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/sbc/2027/spanish/IL27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/sbc/2027/english/MI27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/sbc/2027/spanish/MI27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/sbc/2027/english/SC27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/sbc/2027/spanish/SC27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/sbc/2027/english/FL27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/sbc/2027/spanish/FL27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/english/OH27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/sbc/2027/spanish/OH27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/sbc/2027/english/KY27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/sbc/2027/spanish/KY27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/sbc/2027/english/MS27SBCE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/sbc/2027/spanish/MS27SBCS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/SOB/2027/english/UT27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/SOB/2027/spanish/UT27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/english/IL27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/SOB/2027/spanish/IL27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/english/MI27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/SOB/2027/spanish/MI27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/SOB/2027/english/SC27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/SOB/2027/spanish/SC27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/SOB/2027/english/FL27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/SOB/2027/spanish/FL27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/english/OH27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/SOB/2027/spanish/OH27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/SOB/2027/english/KY27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/SOB/2027/spanish/KY27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/SOB/2027/english/MS27SOBE_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/SOB/2027/spanish/MS27SOBS_G1_0.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/EOC/2027/english/UT27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/EOC/2027/spanish/UT27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/EOC/2027/english/IL27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/il/materials/EOC/2027/spanish/IL27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/EOC/2027/english/MI27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/mi/materials/EOC/2027/spanish/MI27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/EOC/2027/english/SC27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/sc/materials/EOC/2027/spanish/SC27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/EOC/2027/english/FL27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/fl/materials/EOC/2027/spanish/FL27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/EOC/2027/english/OH27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/oh/materials/EOC/2027/spanish/OH27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/EOC/2027/english/KY27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ky/materials/EOC/2027/spanish/KY27EOCS_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/EOC/2027/english/MS27EOCE_OX.pdf</t>
+  </si>
+  <si>
+    <t>https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ms/materials/EOC/2027/spanish/MS27EOCS_OX.pdf</t>
   </si>
 </sst>
 </file>
@@ -6399,11 +6399,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6868,7 +6870,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -6960,7 +6962,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -7052,7 +7054,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
@@ -7144,7 +7146,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B5" t="s">
         <v>86</v>
@@ -7236,7 +7238,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B6" t="s">
         <v>101</v>
@@ -7328,7 +7330,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B7" t="s">
         <v>116</v>
@@ -7420,7 +7422,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B8" t="s">
         <v>131</v>
@@ -7512,7 +7514,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B9" t="s">
         <v>146</v>
@@ -7604,7 +7606,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B10" t="s">
         <v>161</v>
@@ -7696,7 +7698,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B11" t="s">
         <v>176</v>
@@ -9904,7 +9906,7 @@
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B35" t="s">
         <v>536</v>
@@ -9996,7 +9998,7 @@
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B36" t="s">
         <v>550</v>
@@ -10088,7 +10090,7 @@
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B37" t="s">
         <v>561</v>
@@ -10180,7 +10182,7 @@
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B38" t="s">
         <v>572</v>
@@ -10272,7 +10274,7 @@
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B39" t="s">
         <v>583</v>
@@ -10364,7 +10366,7 @@
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B40" t="s">
         <v>594</v>
@@ -10456,7 +10458,7 @@
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B41" t="s">
         <v>605</v>
@@ -10548,7 +10550,7 @@
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B42" t="s">
         <v>616</v>
@@ -10640,7 +10642,7 @@
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B43" t="s">
         <v>627</v>
@@ -10732,7 +10734,7 @@
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B44" t="s">
         <v>638</v>
@@ -11100,7 +11102,7 @@
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B48" t="s">
         <v>682</v>
@@ -11192,7 +11194,7 @@
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B49" t="s">
         <v>700</v>
@@ -11284,7 +11286,7 @@
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B50" t="s">
         <v>711</v>
@@ -11376,7 +11378,7 @@
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B51" t="s">
         <v>722</v>
@@ -11468,7 +11470,7 @@
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B52" t="s">
         <v>733</v>
@@ -11560,7 +11562,7 @@
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B53" t="s">
         <v>744</v>
@@ -11652,7 +11654,7 @@
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B54" t="s">
         <v>755</v>
@@ -11744,7 +11746,7 @@
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B55" t="s">
         <v>766</v>
@@ -11836,7 +11838,7 @@
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B56" t="s">
         <v>777</v>
@@ -11928,7 +11930,7 @@
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B57" t="s">
         <v>788</v>
@@ -12480,7 +12482,7 @@
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B63" t="s">
         <v>854</v>
@@ -12541,21 +12543,6 @@
       </c>
       <c r="U63" t="s">
         <v>870</v>
-      </c>
-      <c r="V63" t="s">
-        <v>54</v>
-      </c>
-      <c r="W63" t="s">
-        <v>54</v>
-      </c>
-      <c r="X63" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>54</v>
       </c>
       <c r="AA63" t="s">
         <v>54</v>
@@ -12572,7 +12559,7 @@
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B64" t="s">
         <v>871</v>
@@ -12633,21 +12620,6 @@
       </c>
       <c r="U64" t="s">
         <v>870</v>
-      </c>
-      <c r="V64" t="s">
-        <v>54</v>
-      </c>
-      <c r="W64" t="s">
-        <v>54</v>
-      </c>
-      <c r="X64" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>54</v>
       </c>
       <c r="AA64" t="s">
         <v>54</v>
@@ -12664,7 +12636,7 @@
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B65" t="s">
         <v>882</v>
@@ -12725,21 +12697,6 @@
       </c>
       <c r="U65" t="s">
         <v>870</v>
-      </c>
-      <c r="V65" t="s">
-        <v>54</v>
-      </c>
-      <c r="W65" t="s">
-        <v>54</v>
-      </c>
-      <c r="X65" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>54</v>
       </c>
       <c r="AA65" t="s">
         <v>54</v>
@@ -12756,7 +12713,7 @@
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B66" t="s">
         <v>893</v>
@@ -12817,21 +12774,6 @@
       </c>
       <c r="U66" t="s">
         <v>870</v>
-      </c>
-      <c r="V66" t="s">
-        <v>54</v>
-      </c>
-      <c r="W66" t="s">
-        <v>54</v>
-      </c>
-      <c r="X66" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>54</v>
       </c>
       <c r="AA66" t="s">
         <v>54</v>
@@ -12848,7 +12790,7 @@
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B67" t="s">
         <v>904</v>
@@ -12909,21 +12851,6 @@
       </c>
       <c r="U67" t="s">
         <v>870</v>
-      </c>
-      <c r="V67" t="s">
-        <v>54</v>
-      </c>
-      <c r="W67" t="s">
-        <v>54</v>
-      </c>
-      <c r="X67" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>54</v>
       </c>
       <c r="AA67" t="s">
         <v>54</v>
@@ -12940,7 +12867,7 @@
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B68" t="s">
         <v>915</v>
@@ -13001,21 +12928,6 @@
       </c>
       <c r="U68" t="s">
         <v>870</v>
-      </c>
-      <c r="V68" t="s">
-        <v>54</v>
-      </c>
-      <c r="W68" t="s">
-        <v>54</v>
-      </c>
-      <c r="X68" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>54</v>
       </c>
       <c r="AA68" t="s">
         <v>54</v>
@@ -13032,7 +12944,7 @@
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B69" t="s">
         <v>926</v>
@@ -13093,21 +13005,6 @@
       </c>
       <c r="U69" t="s">
         <v>870</v>
-      </c>
-      <c r="V69" t="s">
-        <v>54</v>
-      </c>
-      <c r="W69" t="s">
-        <v>54</v>
-      </c>
-      <c r="X69" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>54</v>
       </c>
       <c r="AA69" t="s">
         <v>54</v>
@@ -13124,7 +13021,7 @@
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B70" t="s">
         <v>937</v>
@@ -13185,21 +13082,6 @@
       </c>
       <c r="U70" t="s">
         <v>870</v>
-      </c>
-      <c r="V70" t="s">
-        <v>54</v>
-      </c>
-      <c r="W70" t="s">
-        <v>54</v>
-      </c>
-      <c r="X70" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>54</v>
       </c>
       <c r="AA70" t="s">
         <v>54</v>
@@ -13216,7 +13098,7 @@
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B71" t="s">
         <v>948</v>
@@ -13277,21 +13159,6 @@
       </c>
       <c r="U71" t="s">
         <v>870</v>
-      </c>
-      <c r="V71" t="s">
-        <v>54</v>
-      </c>
-      <c r="W71" t="s">
-        <v>54</v>
-      </c>
-      <c r="X71" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>54</v>
       </c>
       <c r="AA71" t="s">
         <v>54</v>
@@ -13308,7 +13175,7 @@
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B72" t="s">
         <v>959</v>
@@ -13369,21 +13236,6 @@
       </c>
       <c r="U72" t="s">
         <v>870</v>
-      </c>
-      <c r="V72" t="s">
-        <v>54</v>
-      </c>
-      <c r="W72" t="s">
-        <v>54</v>
-      </c>
-      <c r="X72" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>54</v>
       </c>
       <c r="AA72" t="s">
         <v>54</v>
@@ -13462,21 +13314,6 @@
       <c r="U73" t="s">
         <v>870</v>
       </c>
-      <c r="V73" t="s">
-        <v>54</v>
-      </c>
-      <c r="W73" t="s">
-        <v>54</v>
-      </c>
-      <c r="X73" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>54</v>
-      </c>
       <c r="AA73" t="s">
         <v>54</v>
       </c>
@@ -13554,21 +13391,6 @@
       <c r="U74" t="s">
         <v>870</v>
       </c>
-      <c r="V74" t="s">
-        <v>54</v>
-      </c>
-      <c r="W74" t="s">
-        <v>54</v>
-      </c>
-      <c r="X74" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>54</v>
-      </c>
       <c r="AA74" t="s">
         <v>54</v>
       </c>
@@ -13646,21 +13468,6 @@
       <c r="U75" t="s">
         <v>870</v>
       </c>
-      <c r="V75" t="s">
-        <v>54</v>
-      </c>
-      <c r="W75" t="s">
-        <v>54</v>
-      </c>
-      <c r="X75" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>54</v>
-      </c>
       <c r="AA75" t="s">
         <v>54</v>
       </c>
@@ -13738,21 +13545,6 @@
       <c r="U76" t="s">
         <v>870</v>
       </c>
-      <c r="V76" t="s">
-        <v>54</v>
-      </c>
-      <c r="W76" t="s">
-        <v>54</v>
-      </c>
-      <c r="X76" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>54</v>
-      </c>
       <c r="AA76" t="s">
         <v>54</v>
       </c>
@@ -13830,21 +13622,6 @@
       <c r="U77" t="s">
         <v>870</v>
       </c>
-      <c r="V77" t="s">
-        <v>54</v>
-      </c>
-      <c r="W77" t="s">
-        <v>54</v>
-      </c>
-      <c r="X77" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>54</v>
-      </c>
       <c r="AA77" t="s">
         <v>54</v>
       </c>
@@ -13922,21 +13699,6 @@
       <c r="U78" t="s">
         <v>870</v>
       </c>
-      <c r="V78" t="s">
-        <v>54</v>
-      </c>
-      <c r="W78" t="s">
-        <v>54</v>
-      </c>
-      <c r="X78" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>54</v>
-      </c>
       <c r="AA78" t="s">
         <v>54</v>
       </c>
@@ -14014,21 +13776,6 @@
       <c r="U79" t="s">
         <v>870</v>
       </c>
-      <c r="V79" t="s">
-        <v>54</v>
-      </c>
-      <c r="W79" t="s">
-        <v>54</v>
-      </c>
-      <c r="X79" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y79" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>54</v>
-      </c>
       <c r="AA79" t="s">
         <v>54</v>
       </c>
@@ -14106,21 +13853,6 @@
       <c r="U80" t="s">
         <v>870</v>
       </c>
-      <c r="V80" t="s">
-        <v>54</v>
-      </c>
-      <c r="W80" t="s">
-        <v>54</v>
-      </c>
-      <c r="X80" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y80" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>54</v>
-      </c>
       <c r="AA80" t="s">
         <v>54</v>
       </c>
@@ -14198,21 +13930,6 @@
       <c r="U81" t="s">
         <v>870</v>
       </c>
-      <c r="V81" t="s">
-        <v>54</v>
-      </c>
-      <c r="W81" t="s">
-        <v>54</v>
-      </c>
-      <c r="X81" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y81" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>54</v>
-      </c>
       <c r="AA81" t="s">
         <v>54</v>
       </c>
@@ -14290,21 +14007,6 @@
       <c r="U82" t="s">
         <v>870</v>
       </c>
-      <c r="V82" t="s">
-        <v>54</v>
-      </c>
-      <c r="W82" t="s">
-        <v>54</v>
-      </c>
-      <c r="X82" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y82" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>54</v>
-      </c>
       <c r="AA82" t="s">
         <v>54</v>
       </c>
@@ -14382,21 +14084,6 @@
       <c r="U83" t="s">
         <v>870</v>
       </c>
-      <c r="V83" t="s">
-        <v>54</v>
-      </c>
-      <c r="W83" t="s">
-        <v>54</v>
-      </c>
-      <c r="X83" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y83" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>54</v>
-      </c>
       <c r="AA83" t="s">
         <v>54</v>
       </c>
@@ -14474,21 +14161,6 @@
       <c r="U84" t="s">
         <v>870</v>
       </c>
-      <c r="V84" t="s">
-        <v>54</v>
-      </c>
-      <c r="W84" t="s">
-        <v>54</v>
-      </c>
-      <c r="X84" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y84" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>54</v>
-      </c>
       <c r="AA84" t="s">
         <v>54</v>
       </c>
@@ -14566,21 +14238,6 @@
       <c r="U85" t="s">
         <v>870</v>
       </c>
-      <c r="V85" t="s">
-        <v>54</v>
-      </c>
-      <c r="W85" t="s">
-        <v>54</v>
-      </c>
-      <c r="X85" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y85" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>54</v>
-      </c>
       <c r="AA85" t="s">
         <v>54</v>
       </c>
@@ -14658,21 +14315,6 @@
       <c r="U86" t="s">
         <v>870</v>
       </c>
-      <c r="V86" t="s">
-        <v>54</v>
-      </c>
-      <c r="W86" t="s">
-        <v>54</v>
-      </c>
-      <c r="X86" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y86" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>54</v>
-      </c>
       <c r="AA86" t="s">
         <v>54</v>
       </c>
@@ -14750,21 +14392,6 @@
       <c r="U87" t="s">
         <v>870</v>
       </c>
-      <c r="V87" t="s">
-        <v>54</v>
-      </c>
-      <c r="W87" t="s">
-        <v>54</v>
-      </c>
-      <c r="X87" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y87" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>54</v>
-      </c>
       <c r="AA87" t="s">
         <v>54</v>
       </c>
@@ -14842,21 +14469,6 @@
       <c r="U88" t="s">
         <v>870</v>
       </c>
-      <c r="V88" t="s">
-        <v>54</v>
-      </c>
-      <c r="W88" t="s">
-        <v>54</v>
-      </c>
-      <c r="X88" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y88" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>54</v>
-      </c>
       <c r="AA88" t="s">
         <v>54</v>
       </c>
@@ -14872,7 +14484,7 @@
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B89" t="s">
         <v>1146</v>
@@ -14964,7 +14576,7 @@
     </row>
     <row r="90" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B90" t="s">
         <v>1162</v>
@@ -15056,7 +14668,7 @@
     </row>
     <row r="91" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B91" t="s">
         <v>1172</v>
@@ -15148,7 +14760,7 @@
     </row>
     <row r="92" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B92" t="s">
         <v>1182</v>
@@ -15240,7 +14852,7 @@
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B93" t="s">
         <v>1192</v>
@@ -15332,7 +14944,7 @@
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B94" t="s">
         <v>1202</v>
@@ -15424,7 +15036,7 @@
     </row>
     <row r="95" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B95" t="s">
         <v>1212</v>
@@ -15516,7 +15128,7 @@
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B96" t="s">
         <v>1222</v>
@@ -15608,7 +15220,7 @@
     </row>
     <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B97" t="s">
         <v>1232</v>
@@ -15700,7 +15312,7 @@
     </row>
     <row r="98" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B98" t="s">
         <v>1242</v>
@@ -16160,7 +15772,7 @@
     </row>
     <row r="103" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B103" t="s">
         <v>1304</v>
@@ -16252,7 +15864,7 @@
     </row>
     <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B104" t="s">
         <v>1314</v>
@@ -16344,7 +15956,7 @@
     </row>
     <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B105" t="s">
         <v>1324</v>
@@ -16436,7 +16048,7 @@
     </row>
     <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B106" t="s">
         <v>1334</v>
@@ -16528,7 +16140,7 @@
     </row>
     <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B107" t="s">
         <v>1344</v>
@@ -16620,7 +16232,7 @@
     </row>
     <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B108" t="s">
         <v>1354</v>
@@ -16712,7 +16324,7 @@
     </row>
     <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B109" t="s">
         <v>1365</v>
@@ -16804,7 +16416,7 @@
     </row>
     <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B110" t="s">
         <v>1376</v>
@@ -16896,7 +16508,7 @@
     </row>
     <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B111" t="s">
         <v>1387</v>
@@ -16988,7 +16600,7 @@
     </row>
     <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B112" t="s">
         <v>1398</v>
@@ -19380,7 +18992,7 @@
     </row>
     <row r="138" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B138" t="s">
         <v>1679</v>
@@ -19472,7 +19084,7 @@
     </row>
     <row r="139" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B139" t="s">
         <v>1689</v>
@@ -19564,7 +19176,7 @@
     </row>
     <row r="140" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B140" t="s">
         <v>1699</v>
@@ -19656,7 +19268,7 @@
     </row>
     <row r="141" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B141" t="s">
         <v>1710</v>
@@ -19748,7 +19360,7 @@
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B142" t="s">
         <v>1721</v>
@@ -19840,7 +19452,7 @@
     </row>
     <row r="143" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B143" t="s">
         <v>1732</v>
@@ -19932,7 +19544,7 @@
     </row>
     <row r="144" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B144" t="s">
         <v>1743</v>
@@ -20024,7 +19636,7 @@
     </row>
     <row r="145" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B145" t="s">
         <v>1754</v>
@@ -20116,7 +19728,7 @@
     </row>
     <row r="146" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B146" t="s">
         <v>1765</v>
@@ -20208,7 +19820,7 @@
     </row>
     <row r="147" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>30</v>
+        <v>2055</v>
       </c>
       <c r="B147" t="s">
         <v>1776</v>
@@ -21890,10 +21502,10 @@
       <c r="I165" t="s">
         <v>1977</v>
       </c>
-      <c r="J165" s="1" t="s">
+      <c r="J165" s="4" t="s">
         <v>2056</v>
       </c>
-      <c r="K165" t="s">
+      <c r="K165" s="5" t="s">
         <v>2057</v>
       </c>
       <c r="L165" t="s">
@@ -21905,11 +21517,11 @@
       <c r="N165" t="s">
         <v>1979</v>
       </c>
-      <c r="O165" t="s">
-        <v>2058</v>
-      </c>
-      <c r="P165" t="s">
-        <v>2059</v>
+      <c r="O165" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="P165" s="2" t="s">
+        <v>2073</v>
       </c>
       <c r="Q165" t="s">
         <v>1975</v>
@@ -21921,10 +21533,10 @@
         <v>1981</v>
       </c>
       <c r="T165" t="s">
-        <v>2060</v>
+        <v>2088</v>
       </c>
       <c r="U165" t="s">
-        <v>2061</v>
+        <v>2089</v>
       </c>
       <c r="V165" t="s">
         <v>54</v>
@@ -21982,11 +21594,11 @@
       <c r="I166" t="s">
         <v>1988</v>
       </c>
-      <c r="J166" t="s">
-        <v>2062</v>
-      </c>
-      <c r="K166" t="s">
-        <v>2063</v>
+      <c r="J166" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="K166" s="5" t="s">
+        <v>2059</v>
       </c>
       <c r="L166" t="s">
         <v>1975</v>
@@ -21997,11 +21609,11 @@
       <c r="N166" t="s">
         <v>1990</v>
       </c>
-      <c r="O166" t="s">
-        <v>2064</v>
-      </c>
-      <c r="P166" t="s">
-        <v>2065</v>
+      <c r="O166" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="P166" s="2" t="s">
+        <v>2075</v>
       </c>
       <c r="Q166" t="s">
         <v>1975</v>
@@ -22013,10 +21625,10 @@
         <v>1992</v>
       </c>
       <c r="T166" t="s">
-        <v>2066</v>
+        <v>2090</v>
       </c>
       <c r="U166" t="s">
-        <v>2067</v>
+        <v>2091</v>
       </c>
       <c r="V166" t="s">
         <v>54</v>
@@ -22074,11 +21686,11 @@
       <c r="I167" t="s">
         <v>1998</v>
       </c>
-      <c r="J167" t="s">
-        <v>2068</v>
-      </c>
-      <c r="K167" t="s">
-        <v>2069</v>
+      <c r="J167" s="5" t="s">
+        <v>2060</v>
+      </c>
+      <c r="K167" s="5" t="s">
+        <v>2061</v>
       </c>
       <c r="L167" t="s">
         <v>1975</v>
@@ -22089,11 +21701,11 @@
       <c r="N167" t="s">
         <v>2000</v>
       </c>
-      <c r="O167" t="s">
-        <v>2070</v>
-      </c>
-      <c r="P167" t="s">
-        <v>2071</v>
+      <c r="O167" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="P167" s="2" t="s">
+        <v>2077</v>
       </c>
       <c r="Q167" t="s">
         <v>1975</v>
@@ -22105,10 +21717,10 @@
         <v>2002</v>
       </c>
       <c r="T167" t="s">
-        <v>2072</v>
+        <v>2092</v>
       </c>
       <c r="U167" t="s">
-        <v>2073</v>
+        <v>2093</v>
       </c>
       <c r="V167" t="s">
         <v>54</v>
@@ -22166,11 +21778,11 @@
       <c r="I168" t="s">
         <v>2008</v>
       </c>
-      <c r="J168" t="s">
-        <v>2074</v>
-      </c>
-      <c r="K168" t="s">
-        <v>2075</v>
+      <c r="J168" s="5" t="s">
+        <v>2062</v>
+      </c>
+      <c r="K168" s="5" t="s">
+        <v>2063</v>
       </c>
       <c r="L168" t="s">
         <v>1975</v>
@@ -22181,11 +21793,11 @@
       <c r="N168" t="s">
         <v>2010</v>
       </c>
-      <c r="O168" t="s">
-        <v>2076</v>
-      </c>
-      <c r="P168" t="s">
-        <v>2077</v>
+      <c r="O168" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="P168" s="2" t="s">
+        <v>2079</v>
       </c>
       <c r="Q168" t="s">
         <v>1975</v>
@@ -22197,10 +21809,10 @@
         <v>2012</v>
       </c>
       <c r="T168" t="s">
-        <v>2078</v>
+        <v>2094</v>
       </c>
       <c r="U168" t="s">
-        <v>2079</v>
+        <v>2095</v>
       </c>
       <c r="V168" t="s">
         <v>54</v>
@@ -22258,11 +21870,11 @@
       <c r="I169" t="s">
         <v>2018</v>
       </c>
-      <c r="J169" t="s">
-        <v>2080</v>
-      </c>
-      <c r="K169" t="s">
-        <v>2081</v>
+      <c r="J169" s="5" t="s">
+        <v>2064</v>
+      </c>
+      <c r="K169" s="5" t="s">
+        <v>2065</v>
       </c>
       <c r="L169" t="s">
         <v>1975</v>
@@ -22273,11 +21885,11 @@
       <c r="N169" t="s">
         <v>2020</v>
       </c>
-      <c r="O169" t="s">
-        <v>2082</v>
-      </c>
-      <c r="P169" t="s">
-        <v>2083</v>
+      <c r="O169" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="P169" s="2" t="s">
+        <v>2081</v>
       </c>
       <c r="Q169" t="s">
         <v>1975</v>
@@ -22289,10 +21901,10 @@
         <v>2022</v>
       </c>
       <c r="T169" t="s">
-        <v>2084</v>
+        <v>2096</v>
       </c>
       <c r="U169" t="s">
-        <v>2085</v>
+        <v>2097</v>
       </c>
       <c r="V169" t="s">
         <v>54</v>
@@ -22350,11 +21962,11 @@
       <c r="I170" t="s">
         <v>2028</v>
       </c>
-      <c r="J170" t="s">
-        <v>2086</v>
-      </c>
-      <c r="K170" t="s">
-        <v>2087</v>
+      <c r="J170" s="5" t="s">
+        <v>2066</v>
+      </c>
+      <c r="K170" s="5" t="s">
+        <v>2067</v>
       </c>
       <c r="L170" t="s">
         <v>1975</v>
@@ -22365,11 +21977,11 @@
       <c r="N170" t="s">
         <v>2030</v>
       </c>
-      <c r="O170" t="s">
-        <v>2088</v>
-      </c>
-      <c r="P170" t="s">
-        <v>2089</v>
+      <c r="O170" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P170" s="2" t="s">
+        <v>2083</v>
       </c>
       <c r="Q170" t="s">
         <v>1975</v>
@@ -22381,10 +21993,10 @@
         <v>2032</v>
       </c>
       <c r="T170" t="s">
-        <v>2090</v>
+        <v>2098</v>
       </c>
       <c r="U170" t="s">
-        <v>2091</v>
+        <v>2099</v>
       </c>
       <c r="V170" t="s">
         <v>54</v>
@@ -22442,11 +22054,11 @@
       <c r="I171" t="s">
         <v>2039</v>
       </c>
-      <c r="J171" t="s">
-        <v>2092</v>
-      </c>
-      <c r="K171" t="s">
-        <v>2093</v>
+      <c r="J171" s="5" t="s">
+        <v>2068</v>
+      </c>
+      <c r="K171" s="5" t="s">
+        <v>2069</v>
       </c>
       <c r="L171" t="s">
         <v>1975</v>
@@ -22457,11 +22069,11 @@
       <c r="N171" t="s">
         <v>2041</v>
       </c>
-      <c r="O171" t="s">
-        <v>2094</v>
-      </c>
-      <c r="P171" t="s">
-        <v>2095</v>
+      <c r="O171" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="P171" s="2" t="s">
+        <v>2085</v>
       </c>
       <c r="Q171" t="s">
         <v>1975</v>
@@ -22473,10 +22085,10 @@
         <v>2043</v>
       </c>
       <c r="T171" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="U171" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="V171" t="s">
         <v>54</v>
@@ -22534,11 +22146,11 @@
       <c r="I172" t="s">
         <v>2049</v>
       </c>
-      <c r="J172" t="s">
-        <v>2098</v>
-      </c>
-      <c r="K172" t="s">
-        <v>2099</v>
+      <c r="J172" s="5" t="s">
+        <v>2070</v>
+      </c>
+      <c r="K172" s="5" t="s">
+        <v>2071</v>
       </c>
       <c r="L172" t="s">
         <v>1975</v>
@@ -22549,11 +22161,11 @@
       <c r="N172" t="s">
         <v>2051</v>
       </c>
-      <c r="O172" t="s">
-        <v>2100</v>
-      </c>
-      <c r="P172" t="s">
-        <v>2101</v>
+      <c r="O172" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="P172" s="2" t="s">
+        <v>2087</v>
       </c>
       <c r="Q172" t="s">
         <v>1975</v>
@@ -22603,12 +22215,12 @@
   <hyperlinks>
     <hyperlink ref="AD165" r:id="rId1" xr:uid="{AC5603BE-EFE3-4CA2-96E0-F946A8894D30}"/>
     <hyperlink ref="AD166:AD172" r:id="rId2" display="https://uat-pws.molinahealthcare.com/" xr:uid="{C10BB269-8BF9-4251-A8EC-5DF8C1E3DF61}"/>
-    <hyperlink ref="J165" r:id="rId3" display="https://www.molinahealthcare.com/-/media/project/pws/healthcare/pdf/pdf/ifp/ut/materials/sbc/2027/english/UT27SBCE_G1_0.pdf" xr:uid="{C4D7216F-578A-42A5-8993-805593874C4F}"/>
-    <hyperlink ref="J54" r:id="rId4" xr:uid="{EDC94E02-241F-42DC-9985-6C648668A4E4}"/>
+    <hyperlink ref="J54" r:id="rId3" xr:uid="{EDC94E02-241F-42DC-9985-6C648668A4E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AD1 B172:I172 B165:I165 B63:AD164 B48:I48 B49:I62 B35:AD47 B2:AD2 B3:AD34 L165:N165 Q165:S165 V165:AC165 B166:I166 L166:N166 Q166:S166 V166:AC166 B167:I167 L167:N167 Q167:S167 V167:AC167 B168:I168 L168:N168 Q168:S168 V168:AC168 B169:I169 L169:N169 Q169:S169 V169:AC169 B170:I170 L170:N170 Q170:S170 V170:AC170 B171:I171 L171:N171 Q171:S171 V171:AC171 L172:N172 Q172:S172 V172:AC172 K48:AD48 K49:AD62" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AD1 B172:I172 B165:I165 B89:AD164 B48:I48 B49:I62 B35:AD47 B2:U2 B3:U34 L165:N165 Q165:S165 V165:AC165 B166:I166 L166:N166 Q166:S166 V166:AC166 B167:I167 L167:N167 Q167:S167 V167:AC167 B168:I168 L168:N168 Q168:S168 V168:AC168 B169:I169 L169:N169 Q169:S169 V169:AC169 B170:I170 L170:N170 Q170:S170 V170:AC170 B171:I171 L171:N171 Q171:S171 V171:AC171 L172:N172 Q172:S172 V172:AC172 K48:AD48 K49:AD62 AA2:AD2 AA3:AD34 B63:U88 AA63:AD88" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
